--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_maule.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:25</t>
+    <t xml:space="preserve">2026-09-10 01:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_maule.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:40</t>
+    <t xml:space="preserve">2026-09-18 11:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_maule.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:36</t>
+    <t xml:space="preserve">2026-09-23 15:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_maule.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:42</t>
+    <t xml:space="preserve">2026-10-05 16:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -992,7 +992,7 @@
         <v>48.26</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>70.62</v>
+        <v>70.63</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>99.41</v>
